--- a/data/gravel/Esker Lorax 2025.xlsx
+++ b/data/gravel/Esker Lorax 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30080364-2C1F-F842-B9E3-B91459758219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D527DA3-31C9-8944-BF7A-432AFE9ED999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6500" yWindow="500" windowWidth="26940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="500" windowWidth="26940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -362,9 +362,6 @@
     <t>fork_sag</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>carbon</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>Lorax</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -536,9 +536,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -878,42 +878,41 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="22">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="F8" s="15"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -923,20 +922,23 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>537</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>560</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>587</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>610</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="9"/>
@@ -948,19 +950,19 @@
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>365</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>380</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <v>390</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>405</v>
       </c>
       <c r="J10" s="8"/>
@@ -973,19 +975,19 @@
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <v>600</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <v>610</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <v>645</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>670</v>
       </c>
       <c r="J11" s="8"/>
@@ -998,19 +1000,19 @@
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <v>68</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <v>68</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <v>68</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <v>68</v>
       </c>
       <c r="J12" s="8"/>
@@ -1023,19 +1025,19 @@
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <v>90</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <v>100</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <v>138</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <v>165</v>
       </c>
       <c r="J13" s="8"/>
@@ -1048,19 +1050,19 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>74</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <v>73.5</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <v>73</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <v>73</v>
       </c>
       <c r="J14" s="8"/>
@@ -1073,19 +1075,19 @@
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <v>400</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>460</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <v>510</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>560</v>
       </c>
       <c r="J15" s="8"/>
@@ -1098,7 +1100,7 @@
       <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C16">
@@ -1117,65 +1119,65 @@
         <f t="shared" si="0"/>
         <v>445</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="G16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:14" ht="20" customHeight="1">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <v>44</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <v>44</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <v>44</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <v>44</v>
       </c>
       <c r="J17" s="8"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
     </row>
     <row r="18" spans="1:14" ht="22">
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>495</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <v>495</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <v>495</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <v>495</v>
       </c>
       <c r="J18" s="8"/>
@@ -1188,19 +1190,19 @@
       <c r="A19" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <v>68</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <v>68</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="14">
         <v>68</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="14">
         <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1216,19 +1218,19 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <v>1075</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="14">
         <v>1094</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="14">
         <v>1118</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="14">
         <v>1143</v>
       </c>
       <c r="J20" s="8"/>
@@ -1241,19 +1243,19 @@
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <v>60</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <v>60</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <v>60</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="14">
         <v>60</v>
       </c>
       <c r="J21" s="8"/>
@@ -1265,6 +1267,18 @@
     <row r="22" spans="1:14" ht="22">
       <c r="A22" s="1" t="s">
         <v>107</v>
+      </c>
+      <c r="C22" s="14">
+        <v>120</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>120</v>
       </c>
       <c r="G22" s="1"/>
       <c r="J22" s="8"/>
@@ -1277,11 +1291,19 @@
       <c r="A23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>30</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>30</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="J23" s="13"/>
       <c r="K23" s="9"/>
@@ -1500,7 +1522,7 @@
         <v>72</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1508,10 +1530,10 @@
         <v>33</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1592,7 +1614,7 @@
         <v>102</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1600,7 +1622,7 @@
         <v>103</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1618,7 +1640,7 @@
         <v>106</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:2">

--- a/data/gravel/Esker Lorax 2025.xlsx
+++ b/data/gravel/Esker Lorax 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D527DA3-31C9-8944-BF7A-432AFE9ED999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37598E98-59E7-2743-B8FF-EAAED2A5BB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="500" windowWidth="26940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,18 +383,6 @@
     <t>chromoly 4130</t>
   </si>
   <si>
-    <t>S1/SM </t>
-  </si>
-  <si>
-    <t>S2/MD </t>
-  </si>
-  <si>
-    <t>S3/LG </t>
-  </si>
-  <si>
-    <t>S4/XL </t>
-  </si>
-  <si>
     <t>445-459</t>
   </si>
   <si>
@@ -405,6 +393,18 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>S1/SM</t>
+  </si>
+  <si>
+    <t>S2/MD</t>
+  </si>
+  <si>
+    <t>S3/LG</t>
+  </si>
+  <si>
+    <t>S4/XL</t>
   </si>
 </sst>
 </file>
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -891,7 +891,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -902,16 +902,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -1120,16 +1120,16 @@
         <v>445</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
@@ -1522,7 +1522,7 @@
         <v>72</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7">
